--- a/Project_CNN/Main/Results/Experimento 9 - ResNet/training_metrics.xlsx
+++ b/Project_CNN/Main/Results/Experimento 9 - ResNet/training_metrics.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Main_Project\ResNet\Results\Experimento 9 - ResNet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\Main\Results\Experimento 9 - ResNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099893FB-5C99-4463-B2E8-8F4617DEA7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D5A171-D1D8-4383-8BF5-372F89B4F31F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
   <si>
     <t>epoch</t>
   </si>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>LR</t>
+  </si>
+  <si>
+    <t>Variante</t>
+  </si>
+  <si>
+    <t>RN34 - BS 64</t>
   </si>
 </sst>
 </file>
@@ -9807,7 +9813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F501"/>
+  <dimension ref="A1:F504"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -19837,6 +19843,47 @@
         <v>1.0370738506317001</v>
       </c>
     </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A503" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C503" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D503" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E503" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F503" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>7</v>
+      </c>
+      <c r="B504">
+        <f>AVERAGE(B487:B501)</f>
+        <v>0.88069028854370202</v>
+      </c>
+      <c r="C504">
+        <f>AVERAGE(C487:C501)</f>
+        <v>0.91590762535731074</v>
+      </c>
+      <c r="E504">
+        <f>AVERAGE(E487:E501)</f>
+        <v>0.87572673956553204</v>
+      </c>
+      <c r="F504">
+        <f>AVERAGE(F487:F501)</f>
+        <v>0.96574305295944185</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
